--- a/insights/20251230-20241230-insights/Anchor_Payroll_history.xlsx
+++ b/insights/20251230-20241230-insights/Anchor_Payroll_history.xlsx
@@ -37,6 +37,60 @@
     <t>D8030</t>
   </si>
   <si>
+    <t>D1030</t>
+  </si>
+  <si>
+    <t>D3050</t>
+  </si>
+  <si>
+    <t>D4031</t>
+  </si>
+  <si>
+    <t>D5110</t>
+  </si>
+  <si>
+    <t>D5113</t>
+  </si>
+  <si>
+    <t>D6030</t>
+  </si>
+  <si>
+    <t>D6740</t>
+  </si>
+  <si>
+    <t>D1100</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5112</t>
+  </si>
+  <si>
+    <t>D6760</t>
+  </si>
+  <si>
+    <t>D8040</t>
+  </si>
+  <si>
+    <t>D1200</t>
+  </si>
+  <si>
+    <t>D5111</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D8050</t>
+  </si>
+  <si>
+    <t>D8060</t>
+  </si>
+  <si>
     <t>D1020</t>
   </si>
   <si>
@@ -46,27 +100,6 @@
     <t>D1070</t>
   </si>
   <si>
-    <t>D1030</t>
-  </si>
-  <si>
-    <t>D3050</t>
-  </si>
-  <si>
-    <t>D4031</t>
-  </si>
-  <si>
-    <t>D5110</t>
-  </si>
-  <si>
-    <t>D5113</t>
-  </si>
-  <si>
-    <t>D6030</t>
-  </si>
-  <si>
-    <t>D6740</t>
-  </si>
-  <si>
     <t>D1010</t>
   </si>
   <si>
@@ -77,39 +110,6 @@
   </si>
   <si>
     <t>D6790</t>
-  </si>
-  <si>
-    <t>D1100</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5112</t>
-  </si>
-  <si>
-    <t>D6760</t>
-  </si>
-  <si>
-    <t>D8040</t>
-  </si>
-  <si>
-    <t>D1200</t>
-  </si>
-  <si>
-    <t>D5111</t>
-  </si>
-  <si>
-    <t>D6215</t>
-  </si>
-  <si>
-    <t>D8050</t>
-  </si>
-  <si>
-    <t>D8060</t>
   </si>
   <si>
     <t>D2000</t>
@@ -555,7 +555,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>1145.59</v>
+        <v>1521.80</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -563,7 +563,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>626.84</v>
+        <v>321.19</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -571,7 +571,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>916.76</v>
+        <v>182.16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -579,7 +579,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>1521.80</v>
+        <v>1055.35</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -587,7 +587,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>321.19</v>
+        <v>619.24</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -595,7 +595,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>182.16</v>
+        <v>568.51</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -603,7 +603,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>1055.35</v>
+        <v>1530.99</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -611,7 +611,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>619.24</v>
+        <v>766.77</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -619,7 +619,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>568.51</v>
+        <v>2839.89</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -627,7 +627,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>1530.99</v>
+        <v>928.53</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -635,7 +635,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>6241.30</v>
+        <v>255.06</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -643,7 +643,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>2531.45</v>
+        <v>868.23</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -651,7 +651,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>898.54</v>
+        <v>870.85</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -659,7 +659,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>763.37</v>
+        <v>3172.27</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -667,7 +667,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>766.77</v>
+        <v>2522.18</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -675,7 +675,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>2839.89</v>
+        <v>374.73</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -683,7 +683,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>928.53</v>
+        <v>208.58</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -691,7 +691,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>255.06</v>
+        <v>495.43</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -699,7 +699,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>868.23</v>
+        <v>1145.59</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -707,7 +707,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>870.85</v>
+        <v>626.84</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -715,7 +715,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>3172.27</v>
+        <v>916.76</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -723,7 +723,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>2522.18</v>
+        <v>6241.30</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -731,7 +731,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>374.73</v>
+        <v>2531.45</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -739,7 +739,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>208.58</v>
+        <v>898.54</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -747,7 +747,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>495.43</v>
+        <v>763.37</v>
       </c>
     </row>
     <row r="33" spans="1:2">
